--- a/Code_py/LAB1.xlsx
+++ b/Code_py/LAB1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andy\Desktop\6to_semestre\Física\Lab\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andy\Desktop\6to_semestre\Fisica\Lab\Codigo\Fisica2_lab\Code_py\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FE0535-5F26-40CC-8962-C6D693462318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118C4EA4-EA3A-4662-903C-B39CC1DB9026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F6FA427C-B52D-4E63-867D-5065B83E5876}"/>
+    <workbookView xWindow="-24120" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{F6FA427C-B52D-4E63-867D-5065B83E5876}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
